--- a/Clientes e Classificações.xlsx
+++ b/Clientes e Classificações.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Maria clara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80A4D554-2785-4698-ABFC-DD847B55AD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87BF6CDB-68ED-4BBB-8197-CE432319CDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{71BC320E-8BFB-4811-8A1D-16882228B8C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{71BC320E-8BFB-4811-8A1D-16882228B8C9}"/>
   </bookViews>
   <sheets>
     <sheet name="CLIENTES" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t>POSIÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$ - </t>
   </si>
   <si>
     <t>D</t>
@@ -171,12 +168,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -218,13 +221,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -545,125 +548,125 @@
   <cols>
     <col min="1" max="1" width="23.85546875" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4">
         <v>3500</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="8" t="str">
         <f>HLOOKUP(B2,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>B</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4">
         <v>1200</v>
       </c>
-      <c r="C3" s="9" t="str">
+      <c r="C3" s="8" t="str">
         <f>HLOOKUP(B3,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>C</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4">
         <v>4500</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="8" t="str">
         <f>HLOOKUP(B4,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>A</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="4">
         <v>750</v>
       </c>
-      <c r="C5" s="9" t="e">
+      <c r="C5" s="8" t="str">
         <f>HLOOKUP(B5,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="4">
         <v>1300</v>
       </c>
-      <c r="C6" s="9" t="str">
+      <c r="C6" s="8" t="str">
         <f>HLOOKUP(B6,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>C</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4">
         <v>9000</v>
       </c>
-      <c r="C7" s="9" t="str">
+      <c r="C7" s="8" t="str">
         <f>HLOOKUP(B7,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>A</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="4">
         <v>1800</v>
       </c>
-      <c r="C8" s="9" t="str">
+      <c r="C8" s="8" t="str">
         <f>HLOOKUP(B8,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>C</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="4">
         <v>2600</v>
       </c>
-      <c r="C9" s="9" t="str">
+      <c r="C9" s="8" t="str">
         <f>HLOOKUP(B9,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>B</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="4">
         <v>3500</v>
       </c>
-      <c r="C10" s="9" t="str">
+      <c r="C10" s="8" t="str">
         <f>HLOOKUP(B10,CLASSIFICAÇÃO!A$1:E$2,2,TRUE)</f>
         <v>B</v>
       </c>
@@ -673,7 +676,7 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -687,15 +690,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <f>MAX(B2:B10)</f>
         <v>9000</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <f>MATCH(B13,B2:B10,0)</f>
         <v>6</v>
       </c>
@@ -704,15 +707,15 @@
         <v>Roseli</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f>MIN(B2:B10)</f>
         <v>750</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <f>MATCH(B14,B2:B10,0)</f>
         <v>4</v>
       </c>
@@ -742,8 +745,8 @@
       <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
+      <c r="B1" s="9">
+        <v>0</v>
       </c>
       <c r="C1" s="4">
         <v>801</v>
@@ -760,16 +763,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
